--- a/template_societes.xlsx
+++ b/template_societes.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +34,27 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
       <sz val="11"/>
     </font>
     <font>
@@ -56,7 +77,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E5A1A"/>
+        <fgColor rgb="00375623"/>
       </patternFill>
     </fill>
   </fills>
@@ -86,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -95,12 +116,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -468,156 +501,168 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NumeroClient</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>RCS</t>
+          <t>NomEntreprise</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>NomEntreprise</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
           <t>Pays</t>
         </is>
       </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>LEI_Existant</t>
+        </is>
+      </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>LEI_Existant</t>
+          <t>LEI_DateValidite</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>LEI_DateValidite</t>
+          <t>CodePostal</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>C00001</t>
+          <t>552 032 534</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>552032534</t>
+          <t>TOTAL SE</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>TOTAL ENERGIES SE</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>529900ODI3047E2LFU29</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>15-01-2026</t>
-        </is>
-      </c>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>C00002</t>
+          <t>HRB 41301</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>1513210151</t>
+          <t>Siemens AG</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>ENTREPRISE EXEMPLE SA</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>C00003</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr"/>
+          <t>B 232 695</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>BNP Paribas S.A.</t>
+        </is>
+      </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>ACME CORPORATION GmbH</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BNPPARISLULL</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>AAAAA0123456789ABCDE</t>
+          <t>31-12-2025</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>L-2449</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>C00004</t>
-        </is>
-      </c>
+      <c r="A5" s="3" t="inlineStr"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>0123456789</t>
+          <t>Arcelor Mittal</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>SOCIÉTÉ TEST SAS</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Example Corp</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>EXAMPLECORP123456</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>15-06-2024</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -630,243 +675,330 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="72" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
+          <t>GLEIF LEI Matcher — Guide d'utilisation</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="6" t="inlineStr"/>
+      <c r="B2" s="7" t="inlineStr"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Colonnes du fichier d'entrée</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
           <t>Colonne</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Description et format attendu</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>NumeroClient</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Identifiant interne de la société dans votre référentiel (texte libre)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>RCS</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Numéro de registre : SIREN/SIRET (FR), HRB (DE), numéro chambre de commerce…
-Préfixe 'RCS Ville' accepté et supprimé automatiquement</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Numéro de registre de commerce / SIREN / HRB / etc. Peut contenir des espaces, tirets et préfixes 'RCS Ville' → la normalisation les supprimera automatiquement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>NomEntreprise</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Nom légal de la société — utilisé pour le matching approché si le RCS échoue</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Nom légal de l'entreprise tel qu'il figure dans votre référentiel. Les formes juridiques (SA, SARL, GmbH…) sont ignorées lors de la comparaison.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Pays</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Pays de domiciliation — ISO alpha-2 (FR, DE, LU…) ou libellé (France, Allemagne…)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Pays du siège social. Accepte le nom complet (France, Allemagne…) ou le code ISO 2 lettres (FR, DE, LU…).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>LEI_Existant</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>[OPTIONNEL] LEI présent dans votre base. Si renseigné :
-  • Validation directe contre GLEIF
-  • Détection de discordance (LEI modifié ou erroné)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>OPTIONNEL — LEI déjà présent dans votre base. Si renseigné, active le mode Validation : le LEI est vérifié dans GLEIF et les divergences (RCS, nom, pays, date, code postal) sont signalées.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>LEI_DateValidite</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>[OPTIONNEL] Date de validité du LEI dans votre base, format dd-mm-yyyy
-  • Comparée avec la date GLEIF (renewal_date)
-  • Écart signalé dans la colonne LEI_Discordance du fichier de sortie</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Logique de traitement</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr"/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>OPTIONNEL — Date de validité du LEI dans votre référentiel. Format attendu : jj-mm-aaaa (ex: 31-12-2025). Comparée avec la date GLEIF ; écart signalé dans LEI_Discordance.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>1. Ligne avec LEI_Existant renseigné</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>→ Validation du LEI contre GLEIF
-   Résultat : LEI Valide / LEI Discordant / Non trouvé (LEI invalide)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>2. Ligne sans LEI_Existant</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>→ Recherche par RCS exact, puis RCS approché (contenance),
-   puis nom + pays approché
-   Résultat : Exact – RCS / Approx – RCS / Approx – Nom/Pays / Non trouvé</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="5" t="inlineStr"/>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>CodePostal</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>OPTIONNEL — Code postal du siège social dans votre référentiel. Utilisé pour affiner le matching nom/pays et contrôler les écarts. Règle de correspondance : les chiffres de votre code postal doivent être contenus dans le code postal GLEIF (ex: '1338' ⊆ 'L-1338'). Fonctionne pour tous les pays (LU, FR, DE, BE…). L'écart est signalé dans la colonne LEI_Discordance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="6" t="inlineStr"/>
+      <c r="B11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Colonnes de sortie générées</t>
+        </is>
+      </c>
       <c r="B12" s="5" t="inlineStr"/>
     </row>
-    <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Colonne LEI_Discordance (sortie)</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Signale TOUS les écarts DQ pour chaque ligne avec correspondance :
-  • LEI manquant → valeur GLEIF proposée
-  • RCS manquant ou différent → valeur GLEIF proposée
-  • Nom légal différent (similarité &lt; seuil)
-  • Date LEI manquante ou différente → valeur GLEIF proposée
-Applicable à tous les types de correspondance, pas uniquement LEI Discordant</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="5" t="inlineStr"/>
-      <c r="B14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Légende couleurs (fichier de sortie)</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Vert foncé</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>LEI validé (cohérent) ou correspondance exacte par RCS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Vert clair</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>RCS approché — caractère manquant dans votre référentiel (ex: zéro de tête)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Jaune</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Correspondance approchée nom + pays</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>LEI Discordant — erreur LEI dans votre base</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Bleu clair</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>LEI invalide — introuvable par LEI, RCS et nom</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Aucune correspondance</t>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Colonne</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>LEI_GLEIF</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Code LEI retourné par la base GLEIF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>GLEIF_NomLegal</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Nom légal de l'entité selon GLEIF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>GLEIF_Pays</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Code pays ISO selon GLEIF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>GLEIF_StatutSociete</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Statut de l'entité (ACTIVE / INACTIVE…).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>GLEIF_StatutLEI</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Statut du LEI (ISSUED / LAPSED…).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>GLEIF_AutoriteRegistre</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Identifiant de l'autorité de registre (RA ID).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>GLEIF_NumRegistre</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Numéro de registre selon GLEIF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>GLEIF_DateRenouvellement</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Date de prochaine échéance LEI selon GLEIF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>TypeCorrespondance</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>LEI Valide / LEI Discordant / Exact – RCS / Approx – RCS / Approx – Nom/Pays / Non trouvé.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>ScoreCorrespondance</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Score de la correspondance. Pour Approx Nom/Pays : 'Nom:xx% / CP:✓' ou 'Nom:xx% / CP:✗'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>LEI_Discordance</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Détail des écarts de data quality : LEI manquant/différent, RCS manquant/différent, Nom différent, Date manquante/différente, Code postal différent. Vide si aucun écart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="6" t="inlineStr"/>
+      <c r="B25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Logique de rapprochement</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Étape 1</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Si LEI_Existant renseigné : lookup direct par LEI dans GLEIF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Étape 2</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Si LEI non trouvé : fallback par RCS exact, puis RCS approché (contenance : '1513210151' ⊆ '01513210151'), puis nom+pays+code postal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Étape 3</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Si LEI non renseigné : RCS exact → RCS approché → nom+pays+code postal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Code postal</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Parmi les candidats nom+pays, préférence pour celui dont le code postal GLEIF contient les chiffres du vôtre. Aucun risque d'exclusion : si aucun candidat ne correspond par CP, le meilleur par nom est retenu.</t>
         </is>
       </c>
     </row>
